--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -32306,7 +32306,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
+          <t>實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790 | 實重:7.6kg | 計重:18.0kg | 類型:E順遞 | 付款:到付月結 | 收件員:131790</t>
         </is>
       </c>
     </row>
